--- a/survey/Survey_Odoo.xlsx
+++ b/survey/Survey_Odoo.xlsx
@@ -1191,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN12"/>
+  <dimension ref="A1:AN13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="24.6640625" customWidth="1" min="1" max="2"/>
@@ -1500,27 +1500,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>image</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>foto</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dirección de referencia</t>
+          <t>Fotos del problema</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Calle principal y secundaria, o un punto conocido cercano</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Opcional. Hasta 3 fotos: ayudan a la cuadrilla a encontrar y dimensionar el problema</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>count-selected(${foto}) &lt;= 3</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Máximo 3 fotos</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>max-pixels=1280</t>
         </is>
       </c>
     </row>
@@ -1532,22 +1547,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ciudad</t>
+          <t>Dirección de referencia</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Calle principal y secundaria, o un punto conocido cercano</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Quito</t>
         </is>
       </c>
     </row>
@@ -1559,22 +1574,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Teléfono de contacto</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Sin espacios ni guiones</t>
+          <t>Ciudad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Quito</t>
         </is>
       </c>
     </row>
@@ -1586,81 +1601,76 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Correo electrónico (opcional)</t>
+          <t>Teléfono de contacto</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sin espacios ni guiones</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>no</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>regex(., '.*@.*\..*')</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Ingresa un correo válido</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>odoo_partner_id</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>odoo_partner_id</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Campo de sistema: lo completa el microservicio de integración, no el ciudadano</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Correo electrónico (opcional)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>regex(., '.*@.*\..*')</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Ingresa un correo válido</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>odoo_partner_id</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>odoo_partner_id</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Campo de sistema: lo completa el microservicio de integración</t>
+          <t>Campo de sistema: lo completa el microservicio de integración, no el ciudadano</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1677,22 +1687,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Campo de sistema: se completa al sincronizar de vuelta con Odoo</t>
+          <t>Campo de sistema: lo completa el microservicio de integración</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1714,25 +1724,57 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Campo de sistema: se completa al sincronizar de vuelta con Odoo</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>longitude</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>longitude</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Campo de sistema: se completa al sincronizar de vuelta con Odoo</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
